--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_366_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_366_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1531,16 +1531,16 @@
         <v>19</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>5</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
@@ -2315,16 +2315,16 @@
         <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>4</v>
@@ -2511,16 +2511,16 @@
         <v>14</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>4</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X24" t="n">
         <v>9</v>
@@ -3043,16 +3043,16 @@
         <v>115</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -3508,16 +3508,16 @@
         <v>29</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X31" t="n">
         <v>1</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>2</v>
@@ -6000,16 +6000,16 @@
         <v>96</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X44" t="n">
         <v>11</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_366_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_366_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>97.14</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2327,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>4</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3055,14 +3055,14 @@
         <v>15</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3520,14 +3520,14 @@
         <v>4</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA31" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6012,14 +6012,14 @@
         <v>5</v>
       </c>
       <c r="X44" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA44" t="n">
